--- a/templates/RELACION_SEMANAL_TIEMPO_EXTRA.xlsx
+++ b/templates/RELACION_SEMANAL_TIEMPO_EXTRA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4b81a271fcbe99b5/Desktop/code/EstrategiaT/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8B3F608-0E7A-4B3A-8472-635ADD4E2242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{B8B3F608-0E7A-4B3A-8472-635ADD4E2242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A482EE2-9E89-4831-B626-8549C9486FD4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2856" yWindow="2856" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="relacion semanal" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>NOMBRE</t>
   </si>
@@ -79,12 +79,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0\ &quot;Empleados&quot;"/>
-    <numFmt numFmtId="165" formatCode="0\ &quot;Horas&quot;"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,13 +109,6 @@
     <font>
       <b/>
       <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -174,7 +166,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -223,15 +215,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="double">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color indexed="64"/>
       </left>
@@ -252,17 +235,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="double">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color indexed="64"/>
       </left>
@@ -331,33 +303,39 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -370,18 +348,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -957,52 +923,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -1024,210 +990,218 @@
     </row>
     <row r="6" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="7" spans="1:24" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="12"/>
-    </row>
-    <row r="8" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="19" t="s">
+      <c r="C7" s="23"/>
+      <c r="D7" s="10"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B8" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="3"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="20"/>
     </row>
     <row r="9" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="23"/>
-      <c r="D9" s="4"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="17"/>
     </row>
     <row r="10" spans="1:24" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="24"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="5"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:24" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="9"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="14"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="12"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="14"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="12"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="14"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="12"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="14"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="12"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="14"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="12"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="14"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="12"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="14"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="12"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="14"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="12"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="14"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="12"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="14"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="12"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="14"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="12"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="14"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="12"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="14"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="12"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="14"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="12"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="14"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="12"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="14"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="12"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="14"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="12"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="14"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="12"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="14"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="12"/>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="14"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="12"/>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="14"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="12"/>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="14"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="12"/>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="14"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="12"/>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D8:E8"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D9:E9"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967294" r:id="rId1"/>
